--- a/business_forms/023_seo_analysis_report_form--business_forms.xlsx
+++ b/business_forms/023_seo_analysis_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>meta_description_length</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Keywords</t>
+          <t>Meta Description Length</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>header_tags</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Header Tags</t>
+          <t>Keywords</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>meta_description_length</t>
+          <t>keywords_length</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meta Description Length</t>
+          <t>Keywords Length</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>keywords_length</t>
+          <t>header_tags</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Keywords Length</t>
+          <t>Header Tags</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>meta_tags_list</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meta Tags List</t>
+          <t>Url</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>meta_description</t>
+          <t>meta_description_duplicate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meta Description</t>
+          <t>Duplicate Meta Tags</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>meta_tags_count</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Keywords</t>
+          <t>Meta Tags Count</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>header_tags</t>
+          <t>meta_description_count</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Header Tags</t>
+          <t>Meta Description Count</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,85 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>meta_description_length</t>
+          <t>keywords_count</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Meta Description Length</t>
+          <t>Keywords Count</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>keywords_length</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Keywords Length</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>header_tags_length</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Header Tags Length</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Url</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -998,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>meta_tags_list_choices</t>
+          <t>meta_description_duplicate_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>meta_tags_list_choices</t>
+          <t>meta_description_duplicate_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1024,74 +955,6 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>keywords_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>keywords_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>header_tags_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>header_tags_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
